--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:43</t>
+    <t xml:space="preserve">2026-09-09 22:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:30</t>
+    <t xml:space="preserve">2026-09-12 19:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
@@ -45,18 +45,21 @@
     <t xml:space="preserve">Mariquina</t>
   </si>
   <si>
+    <t xml:space="preserve">Paillaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Río Bueno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futrono</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Unión</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lago Ranco</t>
   </si>
   <si>
-    <t xml:space="preserve">Futrono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Unión</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paillaco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Los Lagos</t>
   </si>
   <si>
@@ -69,16 +72,13 @@
     <t xml:space="preserve">Corral</t>
   </si>
   <si>
-    <t xml:space="preserve">Río Bueno</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:47</t>
+    <t xml:space="preserve">2026-09-24 00:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -511,7 +511,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>5091</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="3">
@@ -528,7 +528,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>3780</v>
+        <v>995</v>
       </c>
     </row>
     <row r="4">
@@ -545,7 +545,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2465</v>
+        <v>497</v>
       </c>
     </row>
     <row r="5">
@@ -556,13 +556,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>14203</v>
+        <v>14107</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1842</v>
+        <v>406</v>
       </c>
     </row>
     <row r="6">
@@ -573,13 +573,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>14202</v>
+        <v>14204</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1634</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7">
@@ -590,13 +590,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>14201</v>
+        <v>14202</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1537</v>
+        <v>356</v>
       </c>
     </row>
     <row r="8">
@@ -607,13 +607,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>14107</v>
+        <v>14201</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1502</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -624,13 +624,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>14104</v>
+        <v>14203</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1103</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10">
@@ -641,13 +641,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>14103</v>
+        <v>14104</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1040</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -658,13 +658,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>14105</v>
+        <v>14103</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>204</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -675,13 +675,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>14102</v>
+        <v>14105</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>73</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -692,13 +692,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>14204</v>
+        <v>14102</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-1313</v>
+        <v>-35</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:25</t>
+    <t xml:space="preserve">2026-09-27 22:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:13</t>
+    <t xml:space="preserve">2026-10-01 20:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:54</t>
+    <t xml:space="preserve">2026-10-02 13:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2023_los rios.xlsx
@@ -78,7 +78,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:24</t>
+    <t xml:space="preserve">2026-10-05 08:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
